--- a/エプソムカップ予想.xlsx
+++ b/エプソムカップ予想.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yazuyuta/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6152EC9D-617A-DC4C-BD40-F36482F76196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15B7DF92-7AF2-5546-B3F1-9C32A72F4040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6720" yWindow="22300" windowWidth="27040" windowHeight="16860" xr2:uid="{1AF6A17F-30FB-8149-BB42-7FDC863FA778}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{1AF6A17F-30FB-8149-BB42-7FDC863FA778}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="4" r:id="rId2"/>
+    <sheet name="20260507時点" sheetId="5" r:id="rId1"/>
+    <sheet name="Sheet4" sheetId="6" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="181029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,8 +38,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="125">
   <si>
     <t>牡6</t>
   </si>
@@ -874,12 +897,489 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t>編集</t>
+  </si>
+  <si>
+    <t> --◎◯▲△☆&amp;#10003消 </t>
+  </si>
+  <si>
+    <t>前日人気順</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ゼンジツ </t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t xml:space="preserve">ニンキジュン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未定</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ミテイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>S-</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A+</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B＋</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Cー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Bー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B+〜B-</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【逃げ】前で流れに乗れる点は今回のメンバー構成において大きな強み、スロー寄りの展開になれば主導権を握る可能性もある。一定の持続力を持っており、単なる逃げ・先行馬ではなく好位で脚を溜めて運べる点は評価できる。東京芝1800においても、極端な瞬発力勝負にならなければ粘り込みの余地は十分にある。差し脚比べになった際、トップクラスの差し馬に劣る可能性があるが、スロー展開になることを想定し、シルトホルンを軸とした買い方も検討</t>
+    <rPh sb="1" eb="2">
+      <t xml:space="preserve">ニゲ </t>
+    </rPh>
+    <rPh sb="180" eb="182">
+      <t xml:space="preserve">テンカイ </t>
+    </rPh>
+    <rPh sb="188" eb="190">
+      <t xml:space="preserve">ソウテイ </t>
+    </rPh>
+    <rPh sb="199" eb="200">
+      <t xml:space="preserve">ジクト </t>
+    </rPh>
+    <rPh sb="207" eb="209">
+      <t xml:space="preserve">ケントウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>出</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>場しない</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">シュツジョウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【先行】前走は好位から粘る競馬で持続力を示しており、先行して運べる点は今回のメンバーの中でも明確な強み。スローで流れた場合には前残りの展開を作れる可能性があり、位置取りの優位性は大きい。一方で、直線の長い東京では瞬発力勝負になりやすく、差し馬との決め手勝負では分は悪いのは確か。スロー展開となって最後まで残り、3着争いには食い込みそう。</t>
+    <rPh sb="1" eb="3">
+      <t xml:space="preserve">センコウ </t>
+    </rPh>
+    <rPh sb="136" eb="137">
+      <t xml:space="preserve">タシカ </t>
+    </rPh>
+    <rPh sb="148" eb="150">
+      <t xml:space="preserve">サイゴマデ </t>
+    </rPh>
+    <rPh sb="152" eb="153">
+      <t xml:space="preserve">ノコリ </t>
+    </rPh>
+    <rPh sb="156" eb="157">
+      <t xml:space="preserve">チャク </t>
+    </rPh>
+    <rPh sb="157" eb="158">
+      <t xml:space="preserve">アラソイ </t>
+    </rPh>
+    <rPh sb="161" eb="162">
+      <t xml:space="preserve">クイコミ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【先行】重賞戦線での実績があり、地力はメンバー内でも上位。持続力とパワーを活かす競馬が得意で、一定のペースで流れた際にはしぶとく伸びる。
+一方で、直線の長い東京芝1800では瞬発力勝負に寄りやすく、キレ勝負ではトロヴァトーレやジュンブロッサムに見劣る可能性がある。外します！</t>
+    <rPh sb="128" eb="129">
+      <t xml:space="preserve">ハズシマス </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【好位差し】過去にNHKマイルカップで上位争いをしている実績から、メンバー内でも潜在能力は上位。前走の中山記念も走りは悪くなく、0秒5差の6位。爆発力に期待。</t>
+    <rPh sb="1" eb="3">
+      <t xml:space="preserve">コウイ </t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t xml:space="preserve">サシ </t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t xml:space="preserve">ゼンソウ </t>
+    </rPh>
+    <rPh sb="51" eb="55">
+      <t xml:space="preserve">ナカヤマキネン </t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t xml:space="preserve">ハシリハ </t>
+    </rPh>
+    <rPh sb="59" eb="60">
+      <t xml:space="preserve">ワルクナク </t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t xml:space="preserve">ビョウ </t>
+    </rPh>
+    <rPh sb="67" eb="68">
+      <t xml:space="preserve">サ </t>
+    </rPh>
+    <rPh sb="70" eb="71">
+      <t xml:space="preserve">イ </t>
+    </rPh>
+    <rPh sb="72" eb="75">
+      <t xml:space="preserve">バクハツリョク </t>
+    </rPh>
+    <rPh sb="76" eb="78">
+      <t xml:space="preserve">キタイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【好位差し】先行〜差しまで対応できる器用さは評価できるが、突出した強みはなさそうで、どの展開になっても決め手や持続力で上位馬に見劣る可能性が高い。
+大崩れはしにくいものの、勝ち負けラインに入るにはもう一段のパフォーマンスが必要であり、優先度は低い。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【好位差し】クラシック戦線で上位争いをしてきた実績から、メンバー内では能力面で最上位クラスに位置する。特に末脚の持続力と総合力の高さが強みで、単なる瞬発力勝負だけでなく、ある程度流れた展開にも対応できる点は評価できる。直線の長い東京芝1800は条件として合致しやすく、極端な位置取りにならなければ安定して上位争いに加わる可能性が高い。一方で、今回は古馬との対戦に加え、これまでよりもペースや展開の読みが難しい点、合わせて位置取りが後ろに寄りすぎた場合には差し届かないリスクもある。それでもポテンシャルの高さと総合力を重視すれば、かなりの上位評価。</t>
+    <rPh sb="198" eb="199">
+      <t xml:space="preserve">テン </t>
+    </rPh>
+    <rPh sb="200" eb="201">
+      <t xml:space="preserve">アワセテ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【中団】脚質的には中団で運べるため位置取りの自由度が高く、直線の長い東京芝1800でもロスなく立ち回れれば上位進出の余地はあるが、同型の中団差しタイプが多い今回のメンバー構成ではポジション争いで中途半端な位置取りになりそう。総合的には展開が流れて持続力勝負になれば浮上の余地はあるが、勝ち切るイメージまでは持ちづらい。</t>
+    <rPh sb="1" eb="3">
+      <t xml:space="preserve">チュウダン </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【差し】前走『東京新聞杯(G3)』芝1600（左）では上がり最速の末脚を発揮し差し切り勝ち。東京コースでの瞬発力は本レースの勝ちパターンと合致しており、能力の再現性という点ではメンバー中最上位。鞍上も引き続きクリストフ・ルメール騎手である点も安定材料。一方で、今回は1600mから1800mへの距離延長に加え、斤量58kgと条件がやや厳しくなり、終いのキレがわずかに鈍る可能性や位置取り次第では差し届かないリスクも残る。それでも末脚の質と東京適性から大崩れは考えにくく、3着内確実と考える。</t>
+    <rPh sb="1" eb="2">
+      <t xml:space="preserve">サシ </t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t xml:space="preserve">ゼンソウ </t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t xml:space="preserve">トウキョウ </t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t xml:space="preserve">シンブンハイ </t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t xml:space="preserve">シバ </t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t xml:space="preserve">ヒダリ </t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t xml:space="preserve">スエアシ </t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t xml:space="preserve">ハッキシ </t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t xml:space="preserve">サシキリガチ </t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>🏅</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t xml:space="preserve">サシキャクシツ </t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t xml:space="preserve">ムケ </t>
+    </rPh>
+    <rPh sb="56" eb="57">
+      <t xml:space="preserve">キシュモ </t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t xml:space="preserve">ゼンソウ </t>
+    </rPh>
+    <rPh sb="60" eb="62">
+      <t xml:space="preserve">ドウヨウ </t>
+    </rPh>
+    <rPh sb="74" eb="76">
+      <t xml:space="preserve">ジュントウニ </t>
+    </rPh>
+    <rPh sb="77" eb="78">
+      <t xml:space="preserve">カンガエルナラ </t>
+    </rPh>
+    <rPh sb="82" eb="84">
+      <t xml:space="preserve">ホンメイ </t>
+    </rPh>
+    <rPh sb="84" eb="86">
+      <t xml:space="preserve">コウホ </t>
+    </rPh>
+    <rPh sb="87" eb="88">
+      <t xml:space="preserve">チャク </t>
+    </rPh>
+    <rPh sb="88" eb="89">
+      <t xml:space="preserve">ナイ </t>
+    </rPh>
+    <rPh sb="94" eb="96">
+      <t>🕐</t>
+    </rPh>
+    <rPh sb="110" eb="112">
+      <t xml:space="preserve">ショウブ </t>
+    </rPh>
+    <rPh sb="113" eb="115">
+      <t xml:space="preserve">キンリョウ </t>
+    </rPh>
+    <rPh sb="120" eb="122">
+      <t xml:space="preserve">サイゴ </t>
+    </rPh>
+    <rPh sb="123" eb="125">
+      <t xml:space="preserve">チョクセン </t>
+    </rPh>
+    <rPh sb="131" eb="134">
+      <t xml:space="preserve">カノウセイ </t>
+    </rPh>
+    <rPh sb="135" eb="137">
+      <t xml:space="preserve">コウリョ </t>
+    </rPh>
+    <rPh sb="139" eb="141">
+      <t xml:space="preserve">テバナシ </t>
+    </rPh>
+    <rPh sb="141" eb="143">
+      <t xml:space="preserve">イナイ </t>
+    </rPh>
+    <rPh sb="144" eb="146">
+      <t xml:space="preserve">ヨソウ </t>
+    </rPh>
+    <rPh sb="236" eb="237">
+      <t xml:space="preserve">チャク </t>
+    </rPh>
+    <rPh sb="237" eb="238">
+      <t xml:space="preserve">ナイ </t>
+    </rPh>
+    <rPh sb="238" eb="240">
+      <t xml:space="preserve">カクジツ </t>
+    </rPh>
+    <rPh sb="241" eb="242">
+      <t xml:space="preserve">カンガエル </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【差し】これまで中距離重賞戦線で安定して上位争いを続けてきた実績があり、持続力と地力の高さはメンバー内でも上位。しぶとさに定評あり。一方で、これまで長距離2000以上が主な舞台のため、東京芝1800適正は評価しかね、条件適性はやや劣る可能性がある。総合的には能力自体は足りるが、今回の舞台設定ではベスト条件ではないのでは？</t>
+    <rPh sb="70" eb="73">
+      <t xml:space="preserve">チョウキョリ </t>
+    </rPh>
+    <rPh sb="77" eb="79">
+      <t xml:space="preserve">イジョウ </t>
+    </rPh>
+    <rPh sb="80" eb="81">
+      <t xml:space="preserve">オモナ </t>
+    </rPh>
+    <rPh sb="82" eb="84">
+      <t xml:space="preserve">ブタイ </t>
+    </rPh>
+    <rPh sb="95" eb="97">
+      <t xml:space="preserve">テキセイハ </t>
+    </rPh>
+    <rPh sb="98" eb="100">
+      <t xml:space="preserve">ヒョウカ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【中団】一定のペースで流れる展開でパフォーマンスを発揮しやすい。脚質的には中団前後で運べるため、位置取りの自由度があり、極端な展開に左右されにくい点は強みといえる。東京芝1800においてもロスなく立ち回れれば上位進出の余地はある。一方で、直線の長い東京で瞬発力勝負になったとき、トロヴァトーレやジュンブロッサムといったキレのある馬に対しては分が悪そう。また、同型の持続力タイプ（マテンロウレオやセンツブラッド）との比較でも劣るように思われる。DよりのC・・・外します！</t>
+    <rPh sb="1" eb="3">
+      <t xml:space="preserve">チュウダン </t>
+    </rPh>
+    <rPh sb="164" eb="165">
+      <t xml:space="preserve">ウマ </t>
+    </rPh>
+    <rPh sb="211" eb="212">
+      <t xml:space="preserve">オトル </t>
+    </rPh>
+    <rPh sb="216" eb="217">
+      <t xml:space="preserve">オモワレル </t>
+    </rPh>
+    <rPh sb="229" eb="230">
+      <t xml:space="preserve">ハズシマス </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【差し】中断〜後方から脚を使うタイプ？他メンバーと比較したときに上位に来るイメージが湧かない。。。ちょっと怖いですが外します！</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">チュウダン </t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t xml:space="preserve">サシ </t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t xml:space="preserve">コウホウ </t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t xml:space="preserve">アシヲ </t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t xml:space="preserve">ツカウ </t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t xml:space="preserve">ホカメンバートヒカクシタトキニ </t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t xml:space="preserve">ジョウイニ </t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t xml:space="preserve">クルイメージ </t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t xml:space="preserve">ワカナイ </t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t xml:space="preserve">コワイデスガ </t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t xml:space="preserve">ハズシマス </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【追い込み】前走、前々走好走。持続力のある差し脚が武器で、直線の長い東京芝1800は条件的にプラス。ただし後方からの競馬になりやすく、スロー展開では差し届かないリスクがあるなど展開依存度は高い。軸にはしない！</t>
+    <rPh sb="1" eb="2">
+      <t xml:space="preserve">オイコミ </t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t xml:space="preserve">ゼンソウ </t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t xml:space="preserve">ゼンゼンソウ </t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t xml:space="preserve">スキ </t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t xml:space="preserve">ソウ </t>
+    </rPh>
+    <rPh sb="97" eb="98">
+      <t xml:space="preserve">ジクニハ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【追い込み】前走は後方から脚を伸ばす競馬で一定の末脚を見せており、差し脚質自体は今回の条件に合致。ただし決め手の絶対値ではトロヴァトーレやカラマティアノスに劣る可能性が高く、分が悪い。展開が流れて消耗戦になれば浮上の余地はあるが、同型の上位互換が存在する以上、勝ち切るイメージは持ちづらい。今回は外します！</t>
+    <rPh sb="139" eb="141">
+      <t xml:space="preserve">コンカイハ </t>
+    </rPh>
+    <rPh sb="142" eb="143">
+      <t xml:space="preserve">ハズシマス </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【追い込み】前走は中団から脚を使う競馬で内容自体は悪くないが、上がりの絶対値では上位勢と比較して見劣る。展開が流れて差しが一斉に届く形になれば浮上の余地はあるが、、、。
+能力的には足りる可能性はあるものの、展開依存度が高く、優先度は低い</t>
+    <rPh sb="106" eb="109">
+      <t xml:space="preserve">ユウセンド </t>
+    </rPh>
+    <rPh sb="110" eb="111">
+      <t xml:space="preserve">ヒクイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【追い込み】エプソムCの条件には適性が高そう。後方〜中団からの差しが基本となるため、東京芝1800はプラス材料。一方で、位置取りが後ろに偏りやすくスロー展開では差し届かないリスクがある点や、展開に左右される面は否めない。また、マイル中心で結果を出してきたため、1800mで最後まで同じ切れを維持できるかは課題。総合的には脚質は上位であり、展開がカギ。上位安定勢に一歩劣るが入れたい</t>
+    <rPh sb="154" eb="156">
+      <t xml:space="preserve">キャクシツ </t>
+    </rPh>
+    <rPh sb="177" eb="178">
+      <t xml:space="preserve">オトル </t>
+    </rPh>
+    <rPh sb="180" eb="181">
+      <t xml:space="preserve">イレタイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【追い込み】他の差し馬（トロヴァトーレ、ジュンブロッサム、カラマティアノス）と比べるとキレ・持続力の両面で見劣る可能性が高い。また、位置取りが後方寄りになりやすく、スロー展開では差し届かないリスクも大きい。仮に流れたとしても、上位差し馬をまとめて差し切るだけの決め手を示せていない点は課題。総合的には条件が大きく向いても上位争いまでは一歩足りず、相手候補の中でも優先度は低い。（過去実績が微妙なところも材料）</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">ホカノ </t>
+    </rPh>
+    <rPh sb="183" eb="185">
+      <t xml:space="preserve">カコ </t>
+    </rPh>
+    <rPh sb="185" eb="187">
+      <t xml:space="preserve">ジッセキ </t>
+    </rPh>
+    <rPh sb="188" eb="190">
+      <t xml:space="preserve">ビミョウナ </t>
+    </rPh>
+    <rPh sb="195" eb="197">
+      <t xml:space="preserve">ザイリョウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【追い込み】過去に重賞での好走歴があり地力はあるが、近走の安定感には欠ける。差し脚質で東京コース自体は悪くないものの、近走のパフォーマンスを見ると上位勢と比較して一段劣る印象。
+展開がハマれば一発の可能性はある。。まれに起こる好走をここで引く可能性を信じてミラクル枠でエントリー！</t>
+    <rPh sb="104" eb="105">
+      <t xml:space="preserve">オコル </t>
+    </rPh>
+    <rPh sb="107" eb="109">
+      <t xml:space="preserve">コウソウ </t>
+    </rPh>
+    <rPh sb="113" eb="114">
+      <t xml:space="preserve">ヒク </t>
+    </rPh>
+    <rPh sb="115" eb="118">
+      <t xml:space="preserve">カノウセイ </t>
+    </rPh>
+    <rPh sb="119" eb="120">
+      <t xml:space="preserve">シンジテ </t>
+    </rPh>
+    <rPh sb="126" eb="127">
+      <t xml:space="preserve">ワクデ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="18">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1000,8 +1500,31 @@
       <family val="2"/>
       <charset val="128"/>
     </font>
+    <font>
+      <b/>
+      <sz val="17"/>
+      <color rgb="FF555555"/>
+      <name val="メイリオ"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF0033AA"/>
+      <name val="メイリオ"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF444444"/>
+      <name val="メイリオ"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1062,6 +1585,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1095,7 +1624,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1156,9 +1685,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1195,11 +1721,35 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1220,6 +1770,109 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>102183</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>72988</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>1944147</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>186630</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC4FAAD8-2C71-1046-9ECF-93D44EF7483D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1016583" y="15122488"/>
+          <a:ext cx="7302964" cy="3161642"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>452527</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>248160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>1610063</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>72988</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FAFD332B-EBE2-BB45-82C0-A24BDE93A807}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="909727" y="18599660"/>
+          <a:ext cx="7514748" cy="3126827"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1322,8 +1975,68 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1642,6 +2355,1363 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3148C8B-0C98-B746-A798-81172E4E16BF}">
+  <dimension ref="A1:J27"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <cols>
+    <col min="1" max="1" width="5.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" style="5" customWidth="1"/>
+    <col min="3" max="3" width="10" style="5" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="203.28515625" style="5" customWidth="1"/>
+    <col min="11" max="16384" width="10.7109375" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="23">
+      <c r="A1" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="J1" s="31" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="11" customFormat="1" ht="46">
+      <c r="A2" s="7">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7">
+        <v>2</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="9">
+        <v>4.5</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="10">
+        <v>57</v>
+      </c>
+      <c r="I2" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="11" customFormat="1" ht="69">
+      <c r="A3" s="7">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7">
+        <v>1</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="9">
+        <v>5.9</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="10">
+        <v>58</v>
+      </c>
+      <c r="I3" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="J3" s="18" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" s="11" customFormat="1" ht="46">
+      <c r="A4" s="7">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7">
+        <v>3</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="9">
+        <v>8.6</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="10">
+        <v>58</v>
+      </c>
+      <c r="I4" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="J4" s="18" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="11" customFormat="1" ht="46">
+      <c r="A5" s="35">
+        <v>4</v>
+      </c>
+      <c r="B5" s="35">
+        <v>4</v>
+      </c>
+      <c r="C5" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="D5" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="35">
+        <v>13.7</v>
+      </c>
+      <c r="G5" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" s="37">
+        <v>57</v>
+      </c>
+      <c r="I5" s="41" t="s">
+        <v>104</v>
+      </c>
+      <c r="J5" s="39" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="11" customFormat="1" ht="23">
+      <c r="A6" s="7">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7">
+        <v>5</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="7">
+        <v>16.8</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="10">
+        <v>57</v>
+      </c>
+      <c r="I6" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="J6" s="18" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" s="11" customFormat="1" ht="69">
+      <c r="A7" s="7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7">
+        <v>8</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="7">
+        <v>17.2</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="H7" s="14">
+        <v>56</v>
+      </c>
+      <c r="I7" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="J7" s="18" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" s="15" customFormat="1" ht="46">
+      <c r="A8" s="13">
+        <v>7</v>
+      </c>
+      <c r="B8" s="13">
+        <v>7</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="13">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="14">
+        <v>57</v>
+      </c>
+      <c r="I8" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="J8" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" s="11" customFormat="1" ht="46">
+      <c r="A9" s="7">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7">
+        <v>6</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="7">
+        <v>23.3</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="10">
+        <v>57</v>
+      </c>
+      <c r="I9" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="J9" s="18" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" s="15" customFormat="1" ht="46">
+      <c r="A10" s="13">
+        <v>9</v>
+      </c>
+      <c r="B10" s="13">
+        <v>9</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="13">
+        <v>29.2</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H10" s="14">
+        <v>57</v>
+      </c>
+      <c r="I10" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="J10" s="19" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" s="15" customFormat="1" ht="46">
+      <c r="A11" s="7">
+        <v>10</v>
+      </c>
+      <c r="B11" s="13">
+        <v>10</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" s="13">
+        <v>30.3</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="H11" s="14">
+        <v>57</v>
+      </c>
+      <c r="I11" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="J11" s="19" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" s="15" customFormat="1" ht="69">
+      <c r="A12" s="7">
+        <v>11</v>
+      </c>
+      <c r="B12" s="13">
+        <v>12</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="13">
+        <v>30.7</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14">
+        <v>57</v>
+      </c>
+      <c r="I12" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="J12" s="19" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" s="15" customFormat="1" ht="46">
+      <c r="A13" s="7">
+        <v>12</v>
+      </c>
+      <c r="B13" s="13">
+        <v>11</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="13">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="H13" s="14">
+        <v>58</v>
+      </c>
+      <c r="I13" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="J13" s="19" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" s="15" customFormat="1" ht="69">
+      <c r="A14" s="35">
+        <v>13</v>
+      </c>
+      <c r="B14" s="35">
+        <v>13</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="D14" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="35">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="G14" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="H14" s="37">
+        <v>57</v>
+      </c>
+      <c r="I14" s="41" t="s">
+        <v>104</v>
+      </c>
+      <c r="J14" s="39" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" s="40" customFormat="1" ht="46">
+      <c r="A15" s="35">
+        <v>14</v>
+      </c>
+      <c r="B15" s="35">
+        <v>14</v>
+      </c>
+      <c r="C15" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="D15" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" s="35">
+        <v>45.5</v>
+      </c>
+      <c r="G15" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="37">
+        <v>57</v>
+      </c>
+      <c r="I15" s="38" t="s">
+        <v>77</v>
+      </c>
+      <c r="J15" s="39" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" s="40" customFormat="1" ht="23">
+      <c r="A16" s="35">
+        <v>15</v>
+      </c>
+      <c r="B16" s="35">
+        <v>15</v>
+      </c>
+      <c r="C16" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="D16" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="F16" s="35">
+        <v>52.6</v>
+      </c>
+      <c r="G16" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="H16" s="37">
+        <v>57</v>
+      </c>
+      <c r="I16" s="41" t="s">
+        <v>104</v>
+      </c>
+      <c r="J16" s="39" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" s="15" customFormat="1" ht="46">
+      <c r="A17" s="35">
+        <v>16</v>
+      </c>
+      <c r="B17" s="35">
+        <v>16</v>
+      </c>
+      <c r="C17" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="D17" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="F17" s="35">
+        <v>91.4</v>
+      </c>
+      <c r="G17" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="H17" s="37">
+        <v>57</v>
+      </c>
+      <c r="I17" s="41" t="s">
+        <v>104</v>
+      </c>
+      <c r="J17" s="39" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" s="15" customFormat="1" ht="46">
+      <c r="A18" s="7">
+        <v>17</v>
+      </c>
+      <c r="B18" s="13">
+        <v>17</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="F18" s="13">
+        <v>116.1</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="14">
+        <v>57</v>
+      </c>
+      <c r="I18" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="J18" s="19" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" s="40" customFormat="1" ht="23">
+      <c r="A19" s="35">
+        <v>18</v>
+      </c>
+      <c r="B19" s="35">
+        <v>18</v>
+      </c>
+      <c r="C19" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="D19" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="35">
+        <v>292.2</v>
+      </c>
+      <c r="G19" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="H19" s="37">
+        <v>58</v>
+      </c>
+      <c r="I19" s="38" t="s">
+        <v>100</v>
+      </c>
+      <c r="J19" s="39" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="J22" s="16"/>
+    </row>
+    <row r="24" spans="1:10" ht="27">
+      <c r="C24" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="D25" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="D3" r:id="rId1" tooltip="トロヴァトーレ" display="https://db.netkeiba.com/horse/2021105557" xr:uid="{8F0FD971-E416-8947-B3CA-C49C4F084990}"/>
+    <hyperlink ref="D2" r:id="rId2" tooltip="サクラファレル" display="https://db.netkeiba.com/horse/2022104094" xr:uid="{DE6B338A-D199-6548-9C5A-5BA258CCD1E7}"/>
+    <hyperlink ref="D5" r:id="rId3" tooltip="サブマリーナ" display="https://db.netkeiba.com/horse/2021106449" xr:uid="{1D007841-63D8-F943-91DB-472795E24813}"/>
+    <hyperlink ref="D6" r:id="rId4" tooltip="マジックサンズ" display="https://db.netkeiba.com/horse/2022104772" xr:uid="{50D18171-AD4F-4644-81E7-24C0ECB1ECF2}"/>
+    <hyperlink ref="D9" r:id="rId5" tooltip="センツブラッド" display="https://db.netkeiba.com/horse/2022101648" xr:uid="{11EF0EAC-B9FD-4148-A4BE-94A8389AF2E9}"/>
+    <hyperlink ref="D8" r:id="rId6" tooltip="ジュタ" display="https://db.netkeiba.com/horse/2022104813" xr:uid="{B0730327-8E49-C24D-BD59-1C0CD0AB8C11}"/>
+    <hyperlink ref="D7" r:id="rId7" tooltip="ステレンボッシュ" display="https://db.netkeiba.com/horse/2021105743" xr:uid="{A71B56F4-AED1-3245-932D-5D9A93921115}"/>
+    <hyperlink ref="D10" r:id="rId8" tooltip="レガーロデルシエロ" display="https://db.netkeiba.com/horse/2021105661" xr:uid="{C6F6CFC2-567D-F94C-8C60-E47B0C0C2FB8}"/>
+    <hyperlink ref="D11" r:id="rId9" tooltip="マテンロウレオ" display="https://db.netkeiba.com/horse/2019102879" xr:uid="{8ED3893F-A89C-7D4F-97AB-CEE80B6809B1}"/>
+    <hyperlink ref="D12" r:id="rId10" tooltip="シルトホルン" display="https://db.netkeiba.com/horse/2020105424" xr:uid="{CB07B137-8DD8-1A47-948D-F5A0F7873384}"/>
+    <hyperlink ref="D14" r:id="rId11" tooltip="マイネルモーント" display="https://db.netkeiba.com/horse/2020105749" xr:uid="{5CA187EC-4149-7341-99D9-9EB50B0030B5}"/>
+    <hyperlink ref="D15" r:id="rId12" tooltip="ストレイトトーカー" display="https://db.netkeiba.com/horse/2022101669" xr:uid="{2F3C03FC-64DC-544A-A6A8-3978373617DE}"/>
+    <hyperlink ref="D16" r:id="rId13" tooltip="オクタヴィアヌス" display="https://db.netkeiba.com/horse/2020103132" xr:uid="{A734B10A-826C-EC40-B0B0-12DDF3567841}"/>
+    <hyperlink ref="D17" r:id="rId14" tooltip="エピファニー" display="https://db.netkeiba.com/horse/2019105532" xr:uid="{79AABE2B-56C9-C841-912A-9AE109BFB711}"/>
+    <hyperlink ref="D18" r:id="rId15" tooltip="オニャンコポン" display="https://db.netkeiba.com/horse/2019104756" xr:uid="{A294A4DD-D754-5F48-B5E6-966FCB80A0AA}"/>
+    <hyperlink ref="D19" r:id="rId16" tooltip="ビーアストニッシド" display="https://db.netkeiba.com/horse/2019101348" xr:uid="{D5E92BFB-723E-1248-8C66-F8371081A773}"/>
+    <hyperlink ref="D4" r:id="rId17" tooltip="カラマティアノス" display="https://db.netkeiba.com/horse/2022104896" xr:uid="{F984D505-AF43-E448-B650-5F5E4D4A5A3D}"/>
+    <hyperlink ref="D13" r:id="rId18" tooltip="ジュンブロッサム" display="https://db.netkeiba.com/horse/2019105118" xr:uid="{65DCB505-1255-2B42-8EF2-42728226C9F5}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId19"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3B6D84F-97FF-934E-8DB8-885889564002}">
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="27">
+      <c r="A1" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="2">
+        <v>57</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="2"/>
+      <c r="H1" s="3">
+        <v>4</v>
+      </c>
+      <c r="I1" s="4">
+        <v>1</v>
+      </c>
+      <c r="J1" s="33" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K1" s="33"/>
+      <c r="L1" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="22">
+      <c r="A2" s="34"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2">
+        <v>58</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="2"/>
+      <c r="J2" s="3">
+        <v>4.5</v>
+      </c>
+      <c r="K2" s="4">
+        <v>2</v>
+      </c>
+      <c r="L2" s="33" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M2" s="33"/>
+      <c r="N2" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="22">
+      <c r="A3" s="34"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="2">
+        <v>58</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="2"/>
+      <c r="J3" s="3">
+        <v>5.9</v>
+      </c>
+      <c r="K3" s="4">
+        <v>3</v>
+      </c>
+      <c r="L3" s="33" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M3" s="33"/>
+      <c r="N3" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="22">
+      <c r="A4" s="34"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="2">
+        <v>57</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="J4" s="3">
+        <v>8.6</v>
+      </c>
+      <c r="K4" s="4">
+        <v>4</v>
+      </c>
+      <c r="L4" s="33" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M4" s="33"/>
+      <c r="N4" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="22">
+      <c r="A5" s="34"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="2">
+        <v>57</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="4">
+        <v>13.7</v>
+      </c>
+      <c r="K5" s="4">
+        <v>5</v>
+      </c>
+      <c r="L5" s="33" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M5" s="33"/>
+      <c r="N5" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="22">
+      <c r="A6" s="34"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="2">
+        <v>56</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="2"/>
+      <c r="J6" s="4">
+        <v>16.8</v>
+      </c>
+      <c r="K6" s="4">
+        <v>6</v>
+      </c>
+      <c r="L6" s="33" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M6" s="33"/>
+      <c r="N6" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="22">
+      <c r="A7" s="34"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="2">
+        <v>57</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="2"/>
+      <c r="J7" s="4">
+        <v>17.2</v>
+      </c>
+      <c r="K7" s="4">
+        <v>7</v>
+      </c>
+      <c r="L7" s="33" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M7" s="33"/>
+      <c r="N7" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="22">
+      <c r="A8" s="34"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="2">
+        <v>57</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="2"/>
+      <c r="J8" s="4">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="K8" s="4">
+        <v>8</v>
+      </c>
+      <c r="L8" s="33" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M8" s="33"/>
+      <c r="N8" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="22">
+      <c r="A9" s="34"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="2">
+        <v>57</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" s="2"/>
+      <c r="J9" s="4">
+        <v>23.3</v>
+      </c>
+      <c r="K9" s="4">
+        <v>9</v>
+      </c>
+      <c r="L9" s="33" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M9" s="33"/>
+      <c r="N9" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="22">
+      <c r="A10" s="34"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2">
+        <v>57</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="I10" s="2"/>
+      <c r="J10" s="4">
+        <v>29.2</v>
+      </c>
+      <c r="K10" s="4">
+        <v>10</v>
+      </c>
+      <c r="L10" s="33" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M10" s="33"/>
+      <c r="N10" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="22">
+      <c r="A11" s="34"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>57</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="I11" s="2"/>
+      <c r="J11" s="4">
+        <v>30.3</v>
+      </c>
+      <c r="K11" s="4">
+        <v>11</v>
+      </c>
+      <c r="L11" s="33" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M11" s="33"/>
+      <c r="N11" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="22">
+      <c r="A12" s="34"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="2">
+        <v>58</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="I12" s="2"/>
+      <c r="J12" s="4">
+        <v>30.7</v>
+      </c>
+      <c r="K12" s="4">
+        <v>12</v>
+      </c>
+      <c r="L12" s="33" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M12" s="33"/>
+      <c r="N12" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="22">
+      <c r="A13" s="34"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <v>57</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I13" s="2"/>
+      <c r="J13" s="4">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="K13" s="4">
+        <v>13</v>
+      </c>
+      <c r="L13" s="33" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M13" s="33"/>
+      <c r="N13" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="22">
+      <c r="A14" s="34"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="2">
+        <v>57</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I14" s="2"/>
+      <c r="J14" s="4">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="K14" s="4">
+        <v>14</v>
+      </c>
+      <c r="L14" s="33" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M14" s="33"/>
+      <c r="N14" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="22">
+      <c r="A15" s="34"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2">
+        <v>57</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="I15" s="2"/>
+      <c r="J15" s="4">
+        <v>45.5</v>
+      </c>
+      <c r="K15" s="4">
+        <v>15</v>
+      </c>
+      <c r="L15" s="33" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M15" s="33"/>
+      <c r="N15" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="22">
+      <c r="A16" s="34"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" s="2">
+        <v>57</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I16" s="2"/>
+      <c r="J16" s="4">
+        <v>52.6</v>
+      </c>
+      <c r="K16" s="4">
+        <v>16</v>
+      </c>
+      <c r="L16" s="33" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M16" s="33"/>
+      <c r="N16" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="22">
+      <c r="A17" s="34"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" s="2">
+        <v>57</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="I17" s="2"/>
+      <c r="J17" s="4">
+        <v>91.4</v>
+      </c>
+      <c r="K17" s="4">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="B1" r:id="rId1" tooltip="サクラファレル" display="https://db.netkeiba.com/horse/2022104094" xr:uid="{C6A4C556-24DC-5048-82B9-EB14A2529EFB}"/>
+    <hyperlink ref="E1" r:id="rId2" tooltip="レーン" display="https://db.netkeiba.com/jockey/result/recent/05585/" xr:uid="{52B1AA14-CCEB-C44C-A269-D345885CA6A7}"/>
+    <hyperlink ref="F1" r:id="rId3" tooltip="堀" display="https://db.netkeiba.com/trainer/result/recent/01070/" xr:uid="{8A06860E-D5A0-2E47-8814-4958210B9A94}"/>
+    <hyperlink ref="L1" r:id="rId4" display="javascript:void(0);" xr:uid="{90A31E68-D63D-D04F-82E1-F4DD2827DBA3}"/>
+    <hyperlink ref="D2" r:id="rId5" tooltip="トロヴァトーレ" display="https://db.netkeiba.com/horse/2021105557" xr:uid="{A5BB2BD9-2496-EE41-A700-A673B8FE73BD}"/>
+    <hyperlink ref="G2" r:id="rId6" tooltip="ルメール" display="https://db.netkeiba.com/jockey/result/recent/05339/" xr:uid="{96A6BE40-D9C0-F846-8847-BC15500131F5}"/>
+    <hyperlink ref="H2" r:id="rId7" tooltip="鹿戸" display="https://db.netkeiba.com/trainer/result/recent/01097/" xr:uid="{EA0E6DDD-299C-E34A-B97E-0EDDB05FB6C1}"/>
+    <hyperlink ref="N2" r:id="rId8" display="javascript:void(0);" xr:uid="{8123EA15-FFC7-5344-933A-FA8CF062F194}"/>
+    <hyperlink ref="D3" r:id="rId9" tooltip="カラマティアノス" display="https://db.netkeiba.com/horse/2022104896" xr:uid="{5ABFF743-87B9-144A-B465-5120F1A1DB63}"/>
+    <hyperlink ref="G3" r:id="rId10" tooltip="津村" display="https://db.netkeiba.com/jockey/result/recent/01092/" xr:uid="{6540504A-1727-6040-9403-F787B000204F}"/>
+    <hyperlink ref="H3" r:id="rId11" tooltip="奥村武" display="https://db.netkeiba.com/trainer/result/recent/01145/" xr:uid="{400D1565-175F-C54E-A932-FD420158E74C}"/>
+    <hyperlink ref="N3" r:id="rId12" display="javascript:void(0);" xr:uid="{56518B27-8418-1C43-A583-EE26D8B8052D}"/>
+    <hyperlink ref="D4" r:id="rId13" tooltip="サブマリーナ" display="https://db.netkeiba.com/horse/2021106449" xr:uid="{801EFE33-40B0-F34F-A06F-7871DAB796A0}"/>
+    <hyperlink ref="G4" r:id="rId14" tooltip="武豊" display="https://db.netkeiba.com/jockey/result/recent/00666/" xr:uid="{A966FFCC-481A-E442-B850-CF3B85458ECB}"/>
+    <hyperlink ref="H4" r:id="rId15" tooltip="庄野" display="https://db.netkeiba.com/trainer/result/recent/01087/" xr:uid="{DD570375-EEFB-1D42-9317-EBAAB6BDCD5B}"/>
+    <hyperlink ref="N4" r:id="rId16" display="javascript:void(0);" xr:uid="{782C4117-FF1C-4744-B177-7EB6C9E7ACB7}"/>
+    <hyperlink ref="D5" r:id="rId17" tooltip="マジックサンズ" display="https://db.netkeiba.com/horse/2022104772" xr:uid="{D014E908-D13D-C843-8EC6-ED68850421CA}"/>
+    <hyperlink ref="G5" r:id="rId18" tooltip="横山和" display="https://db.netkeiba.com/jockey/result/recent/01140/" xr:uid="{DB7723D5-D20C-1D4C-90BB-31A3584BDC7D}"/>
+    <hyperlink ref="H5" r:id="rId19" tooltip="須貝" display="https://db.netkeiba.com/trainer/result/recent/01105/" xr:uid="{D311142A-BAD6-154D-8DD3-A034249BEDFB}"/>
+    <hyperlink ref="N5" r:id="rId20" display="javascript:void(0);" xr:uid="{53BF7E6F-7582-4F43-920A-FB6C7952BDFA}"/>
+    <hyperlink ref="D6" r:id="rId21" tooltip="ステレンボッシュ" display="https://db.netkeiba.com/horse/2021105743" xr:uid="{CB9C49F8-05E5-B041-93CB-45A299608E36}"/>
+    <hyperlink ref="G6" r:id="rId22" tooltip="戸崎圭" display="https://db.netkeiba.com/jockey/result/recent/05386/" xr:uid="{5C1427AD-DDC5-164D-A31D-4A1848989D68}"/>
+    <hyperlink ref="H6" r:id="rId23" tooltip="宮田" display="https://db.netkeiba.com/trainer/result/recent/01175/" xr:uid="{031DD52E-09ED-4B48-A2F1-55EB8CCDF59D}"/>
+    <hyperlink ref="N6" r:id="rId24" display="javascript:void(0);" xr:uid="{253D05CE-FF6A-9344-8D66-99D50C750B0D}"/>
+    <hyperlink ref="D7" r:id="rId25" tooltip="ジュタ" display="https://db.netkeiba.com/horse/2022104813" xr:uid="{7A21C18E-9653-574C-9EAF-C873F1B7EFB9}"/>
+    <hyperlink ref="G7" r:id="rId26" tooltip="佐々木" display="https://db.netkeiba.com/jockey/result/recent/01197/" xr:uid="{A39846A0-8312-1248-A019-4783C97DC477}"/>
+    <hyperlink ref="H7" r:id="rId27" tooltip="矢作" display="https://db.netkeiba.com/trainer/result/recent/01075/" xr:uid="{5D074FD8-8029-724F-9747-7CC6C45AC694}"/>
+    <hyperlink ref="N7" r:id="rId28" display="javascript:void(0);" xr:uid="{795EAAC6-6E46-7648-9387-F5B4D325653D}"/>
+    <hyperlink ref="D8" r:id="rId29" tooltip="センツブラッド" display="https://db.netkeiba.com/horse/2022101648" xr:uid="{9A4B69A3-DDDA-D048-87F5-3CAEE002E6C8}"/>
+    <hyperlink ref="G8" r:id="rId30" tooltip="横山武" display="https://db.netkeiba.com/jockey/result/recent/01170/" xr:uid="{99E9B1F9-B597-C746-A46B-E88EDCC85E18}"/>
+    <hyperlink ref="H8" r:id="rId31" tooltip="斉藤崇" display="https://db.netkeiba.com/trainer/result/recent/01151/" xr:uid="{EF67CE43-7F6E-6545-A197-53BE2247FEE4}"/>
+    <hyperlink ref="N8" r:id="rId32" display="javascript:void(0);" xr:uid="{F2875281-F41E-C44F-BE26-4F5E3B4F0635}"/>
+    <hyperlink ref="D9" r:id="rId33" tooltip="レガーロデルシエロ" display="https://db.netkeiba.com/horse/2021105661" xr:uid="{EBE1D678-0E68-F948-8CEB-686447C6C732}"/>
+    <hyperlink ref="G9" r:id="rId34" tooltip="岩田康" display="https://db.netkeiba.com/jockey/result/recent/05203/" xr:uid="{C33A212C-F337-8F49-896A-93CEDC602CDF}"/>
+    <hyperlink ref="H9" r:id="rId35" tooltip="栗田" display="https://db.netkeiba.com/trainer/result/recent/01127/" xr:uid="{A15FDFDB-1792-6E48-BC9A-71902262DD49}"/>
+    <hyperlink ref="N9" r:id="rId36" display="javascript:void(0);" xr:uid="{DDE512BE-106A-C943-A944-3D2058DC8E93}"/>
+    <hyperlink ref="D10" r:id="rId37" tooltip="マテンロウレオ" display="https://db.netkeiba.com/horse/2019102879" xr:uid="{FE9A47FE-5AAA-2C44-910F-03E9590F53E3}"/>
+    <hyperlink ref="G10" r:id="rId38" tooltip="横山典" display="https://db.netkeiba.com/jockey/result/recent/00660/" xr:uid="{31EF6A8F-9841-F148-A149-8EFF3899135A}"/>
+    <hyperlink ref="H10" r:id="rId39" tooltip="昆" display="https://db.netkeiba.com/trainer/result/recent/01044/" xr:uid="{12FE4435-57EC-1E42-B888-6D4D3E970A3F}"/>
+    <hyperlink ref="N10" r:id="rId40" display="javascript:void(0);" xr:uid="{FD040C00-B307-7243-BF23-34C395CEADAD}"/>
+    <hyperlink ref="D11" r:id="rId41" tooltip="シルトホルン" display="https://db.netkeiba.com/horse/2020105424" xr:uid="{222A756A-E875-5541-9C05-E17C6A5CBAD0}"/>
+    <hyperlink ref="G11" r:id="rId42" tooltip="大野" display="https://db.netkeiba.com/jockey/result/recent/01096/" xr:uid="{F8585377-789B-834A-B7F7-45DEDDF61A0B}"/>
+    <hyperlink ref="H11" r:id="rId43" tooltip="新開" display="https://db.netkeiba.com/trainer/result/recent/01116/" xr:uid="{A89EC19E-C1B2-6F42-93D5-C3A474E15D20}"/>
+    <hyperlink ref="N11" r:id="rId44" display="javascript:void(0);" xr:uid="{81064CD8-E120-C041-A058-387945D43FB2}"/>
+    <hyperlink ref="D12" r:id="rId45" tooltip="ジュンブロッサム" display="https://db.netkeiba.com/horse/2019105118" xr:uid="{4311672A-CD15-4B49-9527-8BF758852D1C}"/>
+    <hyperlink ref="G12" r:id="rId46" tooltip="荻野極" display="https://db.netkeiba.com/jockey/result/recent/01160/" xr:uid="{DBFE6B2A-F73A-334C-860E-A55DD596FF6F}"/>
+    <hyperlink ref="H12" r:id="rId47" tooltip="友道" display="https://db.netkeiba.com/trainer/result/recent/01061/" xr:uid="{491E48A1-92B8-174F-9A8A-19136496F230}"/>
+    <hyperlink ref="N12" r:id="rId48" display="javascript:void(0);" xr:uid="{DD2E3FCB-50D6-E648-9CCF-B6530E784AEC}"/>
+    <hyperlink ref="D13" r:id="rId49" tooltip="マイネルモーント" display="https://db.netkeiba.com/horse/2020105749" xr:uid="{3FA095ED-153B-054A-A3B2-AA203B746C59}"/>
+    <hyperlink ref="G13" r:id="rId50" tooltip="丹内" display="https://db.netkeiba.com/jockey/result/recent/01091/" xr:uid="{A46D5A4F-B6A1-5E4C-8997-1F6F230F88E7}"/>
+    <hyperlink ref="H13" r:id="rId51" tooltip="高木" display="https://db.netkeiba.com/trainer/result/recent/01088/" xr:uid="{FCA10F76-5F76-EF4C-ADB0-2085222772C1}"/>
+    <hyperlink ref="N13" r:id="rId52" display="javascript:void(0);" xr:uid="{D16E02B5-4F15-424B-87A1-03FFE3752384}"/>
+    <hyperlink ref="D14" r:id="rId53" tooltip="ストレイトトーカー" display="https://db.netkeiba.com/horse/2022101669" xr:uid="{1049A971-4D5C-AD44-9063-B798A2492A47}"/>
+    <hyperlink ref="G14" r:id="rId54" tooltip="田辺" display="https://db.netkeiba.com/jockey/result/recent/01075/" xr:uid="{CF9BBA0B-1320-5D40-AA03-792218129D1F}"/>
+    <hyperlink ref="H14" r:id="rId55" tooltip="岩戸" display="https://db.netkeiba.com/trainer/result/recent/01051/" xr:uid="{99F2F618-FB5E-084F-8E07-7FB7C46B826B}"/>
+    <hyperlink ref="N14" r:id="rId56" display="javascript:void(0);" xr:uid="{52BA07EE-EC5B-0247-A78A-DF9180C3EB3B}"/>
+    <hyperlink ref="D15" r:id="rId57" tooltip="オクタヴィアヌス" display="https://db.netkeiba.com/horse/2020103132" xr:uid="{D144F023-7BD5-A041-8D4D-8E348D77F8E8}"/>
+    <hyperlink ref="G15" r:id="rId58" tooltip="北村宏" display="https://db.netkeiba.com/jockey/result/recent/01043/" xr:uid="{BBFE75CC-1AB8-4E4A-85C2-256826267E5A}"/>
+    <hyperlink ref="H15" r:id="rId59" tooltip="木村" display="https://db.netkeiba.com/trainer/result/recent/01126/" xr:uid="{832FBC88-2E1D-E540-9519-9442E2C64DE7}"/>
+    <hyperlink ref="N15" r:id="rId60" display="javascript:void(0);" xr:uid="{481A6B93-0D29-E94B-844C-ED46A7E04403}"/>
+    <hyperlink ref="D16" r:id="rId61" tooltip="エピファニー" display="https://db.netkeiba.com/horse/2019105532" xr:uid="{640350F5-DE8F-4A46-872C-DBED8F8D7715}"/>
+    <hyperlink ref="G16" r:id="rId62" tooltip="杉原" display="https://db.netkeiba.com/jockey/result/recent/01135/" xr:uid="{1A7A04E7-169B-4B4C-B2A9-D5BAA11367C4}"/>
+    <hyperlink ref="H16" r:id="rId63" tooltip="宮田" display="https://db.netkeiba.com/trainer/result/recent/01175/" xr:uid="{AD7AFF55-FB78-D546-9D15-7BA022458542}"/>
+    <hyperlink ref="N16" r:id="rId64" display="javascript:void(0);" xr:uid="{959F013B-FE4F-F44C-8148-3BA5F15C3A88}"/>
+    <hyperlink ref="D17" r:id="rId65" tooltip="オニャンコポン" display="https://db.netkeiba.com/horse/2019104756" xr:uid="{D3015F6F-7435-3548-876E-6872B198014E}"/>
+    <hyperlink ref="G17" r:id="rId66" tooltip="菅原明" display="https://db.netkeiba.com/jockey/result/recent/01179/" xr:uid="{229041D7-9D72-464F-9E80-F836EB4A1D0D}"/>
+    <hyperlink ref="H17" r:id="rId67" tooltip="小島" display="https://db.netkeiba.com/trainer/result/recent/01068/" xr:uid="{73BE4632-5E96-3947-9FCB-124E79A7C409}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E8AEB5-192B-1A45-8E12-41730A53DBE9}">
   <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
@@ -1658,31 +3728,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="23">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="C1" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="32" t="s">
+      <c r="E1" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="32" t="s">
+      <c r="G1" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="H1" s="32" t="s">
+      <c r="H1" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="I1" s="32" t="s">
+      <c r="I1" s="31" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1706,7 +3776,7 @@
       <c r="G2" s="10">
         <v>58</v>
       </c>
-      <c r="H2" s="26" t="s">
+      <c r="H2" s="25" t="s">
         <v>69</v>
       </c>
       <c r="I2" s="18" t="s">
@@ -1718,7 +3788,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="20" t="s">
         <v>28</v>
       </c>
       <c r="D3" s="12" t="s">
@@ -1733,7 +3803,7 @@
       <c r="G3" s="10">
         <v>57</v>
       </c>
-      <c r="H3" s="27" t="s">
+      <c r="H3" s="26" t="s">
         <v>75</v>
       </c>
       <c r="I3" s="18" t="s">
@@ -1760,7 +3830,7 @@
       <c r="G4" s="10">
         <v>58</v>
       </c>
-      <c r="H4" s="27" t="s">
+      <c r="H4" s="26" t="s">
         <v>75</v>
       </c>
       <c r="I4" s="18" t="s">
@@ -1787,7 +3857,7 @@
       <c r="G5" s="10">
         <v>57</v>
       </c>
-      <c r="H5" s="28" t="s">
+      <c r="H5" s="27" t="s">
         <v>70</v>
       </c>
       <c r="I5" s="18" t="s">
@@ -1814,7 +3884,7 @@
       <c r="G6" s="10">
         <v>57</v>
       </c>
-      <c r="H6" s="27" t="s">
+      <c r="H6" s="26" t="s">
         <v>75</v>
       </c>
       <c r="I6" s="18" t="s">
@@ -1841,7 +3911,7 @@
       <c r="G7" s="10">
         <v>57</v>
       </c>
-      <c r="H7" s="28" t="s">
+      <c r="H7" s="27" t="s">
         <v>70</v>
       </c>
       <c r="I7" s="18" t="s">
@@ -1849,29 +3919,29 @@
       </c>
     </row>
     <row r="8" spans="1:9" s="11" customFormat="1" ht="46">
-      <c r="A8" s="22">
+      <c r="A8" s="21">
         <v>7</v>
       </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="23" t="s">
+      <c r="B8" s="21"/>
+      <c r="C8" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="21">
         <v>20.7</v>
       </c>
-      <c r="F8" s="24" t="s">
+      <c r="F8" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="24">
-        <v>57</v>
-      </c>
-      <c r="H8" s="29" t="s">
+      <c r="G8" s="23">
+        <v>57</v>
+      </c>
+      <c r="H8" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="I8" s="25" t="s">
+      <c r="I8" s="24" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1880,7 +3950,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="7"/>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="20" t="s">
         <v>40</v>
       </c>
       <c r="D9" s="12" t="s">
@@ -1892,10 +3962,10 @@
       <c r="F9" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="14">
         <v>56</v>
       </c>
-      <c r="H9" s="30" t="s">
+      <c r="H9" s="29" t="s">
         <v>74</v>
       </c>
       <c r="I9" s="18" t="s">
@@ -1903,56 +3973,56 @@
       </c>
     </row>
     <row r="10" spans="1:9" s="15" customFormat="1" ht="46">
-      <c r="A10" s="22">
+      <c r="A10" s="21">
         <v>9</v>
       </c>
-      <c r="B10" s="22"/>
-      <c r="C10" s="23" t="s">
+      <c r="B10" s="21"/>
+      <c r="C10" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="23" t="s">
+      <c r="D10" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="21">
         <v>27.4</v>
       </c>
-      <c r="F10" s="24" t="s">
+      <c r="F10" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="24">
-        <v>57</v>
-      </c>
-      <c r="H10" s="29" t="s">
+      <c r="G10" s="23">
+        <v>57</v>
+      </c>
+      <c r="H10" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="I10" s="25" t="s">
+      <c r="I10" s="24" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="15" customFormat="1" ht="69">
-      <c r="A11" s="33">
+      <c r="A11" s="13">
         <v>10</v>
       </c>
-      <c r="B11" s="33"/>
-      <c r="C11" s="21" t="s">
+      <c r="B11" s="13"/>
+      <c r="C11" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="21" t="s">
+      <c r="D11" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="33">
+      <c r="E11" s="13">
         <v>30.2</v>
       </c>
-      <c r="F11" s="20" t="s">
+      <c r="F11" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="G11" s="20">
-        <v>57</v>
-      </c>
-      <c r="H11" s="28" t="s">
+      <c r="G11" s="14">
+        <v>57</v>
+      </c>
+      <c r="H11" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="I11" s="34" t="s">
+      <c r="I11" s="19" t="s">
         <v>90</v>
       </c>
     </row>
@@ -1976,7 +4046,7 @@
       <c r="G12" s="14">
         <v>58</v>
       </c>
-      <c r="H12" s="27" t="s">
+      <c r="H12" s="26" t="s">
         <v>75</v>
       </c>
       <c r="I12" s="19" t="s">
@@ -1988,7 +4058,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="13"/>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="20" t="s">
         <v>49</v>
       </c>
       <c r="D13" s="12" t="s">
@@ -2003,7 +4073,7 @@
       <c r="G13" s="14">
         <v>57</v>
       </c>
-      <c r="H13" s="27" t="s">
+      <c r="H13" s="26" t="s">
         <v>75</v>
       </c>
       <c r="I13" s="19" t="s">
@@ -2030,7 +4100,7 @@
       <c r="G14" s="14">
         <v>57</v>
       </c>
-      <c r="H14" s="28" t="s">
+      <c r="H14" s="27" t="s">
         <v>70</v>
       </c>
       <c r="I14" s="19" t="s">
@@ -2038,56 +4108,56 @@
       </c>
     </row>
     <row r="15" spans="1:9" s="15" customFormat="1" ht="69">
-      <c r="A15" s="22">
+      <c r="A15" s="21">
         <v>14</v>
       </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="23" t="s">
+      <c r="B15" s="21"/>
+      <c r="C15" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="D15" s="23" t="s">
+      <c r="D15" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="21">
         <v>45.7</v>
       </c>
-      <c r="F15" s="24" t="s">
+      <c r="F15" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="G15" s="24">
-        <v>57</v>
-      </c>
-      <c r="H15" s="29" t="s">
+      <c r="G15" s="23">
+        <v>57</v>
+      </c>
+      <c r="H15" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="I15" s="25" t="s">
+      <c r="I15" s="24" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="15" customFormat="1" ht="46">
-      <c r="A16" s="22">
+      <c r="A16" s="21">
         <v>15</v>
       </c>
-      <c r="B16" s="22"/>
-      <c r="C16" s="23" t="s">
+      <c r="B16" s="21"/>
+      <c r="C16" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="D16" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="E16" s="22">
+      <c r="D16" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="21">
         <v>51.6</v>
       </c>
-      <c r="F16" s="24" t="s">
+      <c r="F16" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="G16" s="24">
-        <v>57</v>
-      </c>
-      <c r="H16" s="29" t="s">
+      <c r="G16" s="23">
+        <v>57</v>
+      </c>
+      <c r="H16" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="I16" s="25" t="s">
+      <c r="I16" s="24" t="s">
         <v>92</v>
       </c>
     </row>
@@ -2111,7 +4181,7 @@
       <c r="G17" s="14">
         <v>57</v>
       </c>
-      <c r="H17" s="28" t="s">
+      <c r="H17" s="27" t="s">
         <v>70</v>
       </c>
       <c r="I17" s="19" t="s">
@@ -2138,7 +4208,7 @@
       <c r="G18" s="14">
         <v>57</v>
       </c>
-      <c r="H18" s="31" t="s">
+      <c r="H18" s="30" t="s">
         <v>79</v>
       </c>
       <c r="I18" s="19" t="s">
@@ -2146,29 +4216,29 @@
       </c>
     </row>
     <row r="19" spans="1:9" s="15" customFormat="1" ht="23">
-      <c r="A19" s="22">
+      <c r="A19" s="21">
         <v>18</v>
       </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="23" t="s">
+      <c r="B19" s="21"/>
+      <c r="C19" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="D19" s="23" t="s">
+      <c r="D19" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E19" s="22">
+      <c r="E19" s="21">
         <v>292.2</v>
       </c>
-      <c r="F19" s="24" t="s">
+      <c r="F19" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="G19" s="24">
+      <c r="G19" s="23">
         <v>58</v>
       </c>
-      <c r="H19" s="29" t="s">
+      <c r="H19" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="I19" s="25" t="s">
+      <c r="I19" s="24" t="s">
         <v>94</v>
       </c>
     </row>
@@ -2220,7 +4290,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF5D6ACE-5AF2-494B-9675-0E55145FA576}">
   <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
